--- a/data/trans_bre/IP16B06-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16B06-Estudios-trans_bre.xlsx
@@ -879,7 +879,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-78,5; 0,0</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-78,5; 0,0</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_bre/IP16B06-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16B06-Estudios-trans_bre.xlsx
@@ -879,7 +879,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-78,5; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-78,5; 0,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
